--- a/predictions/lstm-augmented.xlsx
+++ b/predictions/lstm-augmented.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,11 +457,26 @@
           <t>ape</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>custom_ape</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>group_wape</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>wape</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,22 +493,31 @@
         <v>2.411</v>
       </c>
       <c r="E2" t="n">
-        <v>6.603</v>
+        <v>9.848000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>4.191</v>
+        <v>7.436</v>
       </c>
       <c r="G2" t="n">
-        <v>17.568</v>
+        <v>55.299</v>
       </c>
       <c r="H2" t="n">
-        <v>1.738</v>
+        <v>3.084</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.526</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -510,22 +534,31 @@
         <v>0.878</v>
       </c>
       <c r="E3" t="n">
-        <v>4.473</v>
+        <v>2.526</v>
       </c>
       <c r="F3" t="n">
-        <v>3.596</v>
+        <v>1.649</v>
       </c>
       <c r="G3" t="n">
-        <v>12.931</v>
+        <v>2.718</v>
       </c>
       <c r="H3" t="n">
-        <v>4.098</v>
+        <v>1.879</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.701</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12.899</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -542,22 +575,31 @@
         <v>1.953</v>
       </c>
       <c r="E4" t="n">
-        <v>7.575</v>
+        <v>6.313</v>
       </c>
       <c r="F4" t="n">
-        <v>5.622</v>
+        <v>4.361</v>
       </c>
       <c r="G4" t="n">
-        <v>31.608</v>
+        <v>19.016</v>
       </c>
       <c r="H4" t="n">
-        <v>2.879</v>
+        <v>2.233</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.413</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.526</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -574,20 +616,29 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.155</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.155</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.526</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -604,20 +655,29 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>4.118</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4.118</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>16.957</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>15.637</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.526</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -634,20 +694,29 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.518</v>
+        <v>0.751</v>
       </c>
       <c r="F7" t="n">
-        <v>1.518</v>
+        <v>0.751</v>
       </c>
       <c r="G7" t="n">
-        <v>2.305</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.857</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.526</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -664,20 +733,29 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.526</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -705,11 +783,20 @@
       <c r="H9" t="n">
         <v>1</v>
       </c>
+      <c r="I9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.526</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -726,20 +813,29 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4.608</v>
+        <v>2.848</v>
       </c>
       <c r="F10" t="n">
-        <v>4.608</v>
+        <v>2.848</v>
       </c>
       <c r="G10" t="n">
-        <v>21.235</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>2.937</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12.899</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.526</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -756,20 +852,29 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>8.250999999999999</v>
+        <v>7.177</v>
       </c>
       <c r="F11" t="n">
-        <v>8.250999999999999</v>
+        <v>7.177</v>
       </c>
       <c r="G11" t="n">
-        <v>68.077</v>
+        <v>51.507</v>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6.413</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.526</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -786,22 +891,31 @@
         <v>0.486</v>
       </c>
       <c r="E12" t="n">
-        <v>0.128</v>
+        <v>0.117</v>
       </c>
       <c r="F12" t="n">
-        <v>0.358</v>
+        <v>0.369</v>
       </c>
       <c r="G12" t="n">
-        <v>0.128</v>
+        <v>0.136</v>
       </c>
       <c r="H12" t="n">
-        <v>0.737</v>
+        <v>0.759</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.526</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -818,20 +932,29 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.618</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.618</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.382</v>
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>15.637</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.526</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -848,20 +971,29 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>3.883</v>
+        <v>3.775</v>
       </c>
       <c r="F14" t="n">
-        <v>3.883</v>
+        <v>3.775</v>
       </c>
       <c r="G14" t="n">
-        <v>15.081</v>
+        <v>14.252</v>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.857</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.526</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -878,22 +1010,31 @@
         <v>0.054</v>
       </c>
       <c r="E15" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.114</v>
       </c>
       <c r="F15" t="n">
-        <v>0.017</v>
+        <v>0.06</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31</v>
+        <v>1.118</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.526</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -921,11 +1062,20 @@
       <c r="H16" t="n">
         <v>1</v>
       </c>
+      <c r="I16" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.526</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -942,22 +1092,31 @@
         <v>0.092</v>
       </c>
       <c r="E17" t="n">
-        <v>6.92</v>
+        <v>8.101000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>6.828</v>
+        <v>8.009</v>
       </c>
       <c r="G17" t="n">
-        <v>46.618</v>
+        <v>64.145</v>
       </c>
       <c r="H17" t="n">
-        <v>74.23</v>
+        <v>87.074</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8.260999999999999</v>
+      </c>
+      <c r="J17" t="n">
+        <v>12.899</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.526</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -974,22 +1133,31 @@
         <v>1.365</v>
       </c>
       <c r="E18" t="n">
-        <v>9.374000000000001</v>
+        <v>11.106</v>
       </c>
       <c r="F18" t="n">
-        <v>8.009</v>
+        <v>9.741</v>
       </c>
       <c r="G18" t="n">
-        <v>64.14100000000001</v>
+        <v>94.883</v>
       </c>
       <c r="H18" t="n">
-        <v>5.866</v>
+        <v>7.134</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.936</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6.413</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.526</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1006,22 +1174,31 @@
         <v>0.975</v>
       </c>
       <c r="E19" t="n">
-        <v>0.105</v>
+        <v>0.057</v>
       </c>
       <c r="F19" t="n">
-        <v>0.869</v>
+        <v>0.918</v>
       </c>
       <c r="G19" t="n">
-        <v>0.756</v>
+        <v>0.842</v>
       </c>
       <c r="H19" t="n">
-        <v>0.892</v>
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.526</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1038,22 +1215,31 @@
         <v>0.112</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1.857</v>
       </c>
       <c r="F20" t="n">
-        <v>0.112</v>
+        <v>1.746</v>
       </c>
       <c r="G20" t="n">
-        <v>0.012</v>
+        <v>3.047</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>15.637</v>
+      </c>
+      <c r="I20" t="n">
+        <v>15.637</v>
+      </c>
+      <c r="J20" t="n">
+        <v>15.637</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.526</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1070,22 +1256,31 @@
         <v>1.579</v>
       </c>
       <c r="E21" t="n">
-        <v>4.202</v>
+        <v>4.72</v>
       </c>
       <c r="F21" t="n">
-        <v>2.624</v>
+        <v>3.142</v>
       </c>
       <c r="G21" t="n">
-        <v>6.885</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>1.662</v>
+        <v>1.99</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.857</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.526</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>LSTM-AUGMENTED</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1102,16 +1297,25 @@
         <v>1.27</v>
       </c>
       <c r="E22" t="n">
-        <v>0.091</v>
+        <v>0.113</v>
       </c>
       <c r="F22" t="n">
-        <v>1.179</v>
+        <v>1.157</v>
       </c>
       <c r="G22" t="n">
-        <v>1.39</v>
+        <v>1.339</v>
       </c>
       <c r="H22" t="n">
-        <v>0.928</v>
+        <v>0.911</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.526</v>
       </c>
     </row>
   </sheetData>
